--- a/Agile_Template_Synthetic_User_Platform_Formatted_v2.xlsx
+++ b/Agile_Template_Synthetic_User_Platform_Formatted_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/083063859e607894/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F23DEFD5-7EC6-4D6E-AC83-6379A4CEAD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{793625DC-6486-417C-9DE0-AF823E4D0B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,6 @@
     <definedName name="Type">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4" forceFullCalc="1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -351,7 +350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="262">
   <si>
     <t>Planned Sprint</t>
   </si>
@@ -653,9 +652,6 @@
     <t>T-05</t>
   </si>
   <si>
-    <t>Connect backend persona generation to Ollama Llama 3.2</t>
-  </si>
-  <si>
     <t>LLM Integration</t>
   </si>
   <si>
@@ -899,9 +895,6 @@
     <t>I updated the adoption-intent aggregation and display to reflect the generated persona evidence.</t>
   </si>
   <si>
-    <t>Sprint 4</t>
-  </si>
-  <si>
     <t>Mentor explained that the Research Report action should be positioned after the Insight Analytics and validation information so the workflow is clear.</t>
   </si>
   <si>
@@ -921,12 +914,6 @@
   </si>
   <si>
     <t>Mentor explained that local LLM generation should handle temporary failures safely so persona generation does not stop unnecessarily.</t>
-  </si>
-  <si>
-    <t>I connected the backend to Ollama with Llama 3.2 and added retry and error handling for the local LLM generation flow.</t>
-  </si>
-  <si>
-    <t>SL #</t>
   </si>
   <si>
     <t>Sprint #</t>
@@ -1142,7 +1129,13 @@
     <t>Continue using structured output and retries for reliable generation.</t>
   </si>
   <si>
-    <t>I connected the backend to Ollama with Llama 3.2 and added retry/error handling for the local generation flow.</t>
+    <t>Connect backend persona generation to Gorq, Cerebras, Gemini</t>
+  </si>
+  <si>
+    <t>I connected the backend to Gorq, Cerebras, Gemini and added retry and error handling for the local LLM generation flow.</t>
+  </si>
+  <si>
+    <t>I connected the backend to Gorq, Cerebras, Geminiand added retry/error handling for the local generation flow.</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1148,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="167" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1204,6 +1197,12 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1437,7 +1436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1623,6 +1622,12 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1706,6 +1711,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4232,8 +4241,8 @@
       <c r="B9" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>100</v>
+      <c r="C9" s="67" t="s">
+        <v>259</v>
       </c>
       <c r="D9" s="47">
         <v>46231</v>
@@ -4245,7 +4254,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H9" s="38" t="s">
         <v>14</v>
@@ -4304,10 +4313,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>102</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>103</v>
       </c>
       <c r="D10" s="52">
         <v>46231</v>
@@ -4319,7 +4328,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H10" s="38" t="s">
         <v>14</v>
@@ -4378,10 +4387,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>105</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>106</v>
       </c>
       <c r="D11" s="54">
         <v>46247</v>
@@ -4393,7 +4402,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H11" s="38" t="s">
         <v>14</v>
@@ -4452,10 +4461,10 @@
         <v>28</v>
       </c>
       <c r="B12" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="51" t="s">
         <v>108</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>109</v>
       </c>
       <c r="D12" s="52">
         <v>46247</v>
@@ -4467,7 +4476,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H12" s="38" t="s">
         <v>14</v>
@@ -4526,10 +4535,10 @@
         <v>31</v>
       </c>
       <c r="B13" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="51" t="s">
         <v>111</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>112</v>
       </c>
       <c r="D13" s="52">
         <v>46247</v>
@@ -4541,7 +4550,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H13" s="38" t="s">
         <v>14</v>
@@ -4600,10 +4609,10 @@
         <v>33</v>
       </c>
       <c r="B14" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="51" t="s">
         <v>114</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>115</v>
       </c>
       <c r="D14" s="52">
         <v>46247</v>
@@ -4615,7 +4624,7 @@
         <v>13</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="38" t="s">
         <v>14</v>
@@ -4674,10 +4683,10 @@
         <v>35</v>
       </c>
       <c r="B15" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="51" t="s">
         <v>116</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>117</v>
       </c>
       <c r="D15" s="52">
         <v>46247</v>
@@ -4689,7 +4698,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H15" s="38" t="s">
         <v>14</v>
@@ -4748,10 +4757,10 @@
         <v>37</v>
       </c>
       <c r="B16" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="51" t="s">
         <v>119</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>120</v>
       </c>
       <c r="D16" s="52">
         <v>46247</v>
@@ -4763,7 +4772,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H16" s="38" t="s">
         <v>14</v>
@@ -4822,10 +4831,10 @@
         <v>39</v>
       </c>
       <c r="B17" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="51" t="s">
         <v>122</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>123</v>
       </c>
       <c r="D17" s="52">
         <v>46265</v>
@@ -4837,7 +4846,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H17" s="38" t="s">
         <v>14</v>
@@ -4896,10 +4905,10 @@
         <v>41</v>
       </c>
       <c r="B18" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="51" t="s">
         <v>125</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>126</v>
       </c>
       <c r="D18" s="52">
         <v>46265</v>
@@ -4911,7 +4920,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H18" s="38" t="s">
         <v>14</v>
@@ -4970,10 +4979,10 @@
         <v>43</v>
       </c>
       <c r="B19" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="51" t="s">
         <v>128</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>129</v>
       </c>
       <c r="D19" s="52">
         <v>46265</v>
@@ -4985,7 +4994,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H19" s="38" t="s">
         <v>14</v>
@@ -5044,10 +5053,10 @@
         <v>46</v>
       </c>
       <c r="B20" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="51" t="s">
         <v>130</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>131</v>
       </c>
       <c r="D20" s="52">
         <v>46265</v>
@@ -5059,7 +5068,7 @@
         <v>13</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H20" s="38" t="s">
         <v>14</v>
@@ -5118,10 +5127,10 @@
         <v>48</v>
       </c>
       <c r="B21" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="51" t="s">
         <v>133</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>134</v>
       </c>
       <c r="D21" s="52">
         <v>46265</v>
@@ -5133,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H21" s="38" t="s">
         <v>14</v>
@@ -5192,10 +5201,10 @@
         <v>50</v>
       </c>
       <c r="B22" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="51" t="s">
         <v>136</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>137</v>
       </c>
       <c r="D22" s="52">
         <v>46265</v>
@@ -5207,7 +5216,7 @@
         <v>13</v>
       </c>
       <c r="G22" s="49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H22" s="38" t="s">
         <v>14</v>
@@ -5266,10 +5275,10 @@
         <v>52</v>
       </c>
       <c r="B23" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="51" t="s">
         <v>138</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>139</v>
       </c>
       <c r="D23" s="52">
         <v>46279</v>
@@ -5281,7 +5290,7 @@
         <v>13</v>
       </c>
       <c r="G23" s="49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H23" s="38" t="s">
         <v>14</v>
@@ -5340,10 +5349,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="51" t="s">
         <v>141</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>142</v>
       </c>
       <c r="D24" s="52">
         <v>46279</v>
@@ -5355,7 +5364,7 @@
         <v>13</v>
       </c>
       <c r="G24" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H24" s="38" t="s">
         <v>14</v>
@@ -5414,10 +5423,10 @@
         <v>57</v>
       </c>
       <c r="B25" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="51" t="s">
         <v>144</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>145</v>
       </c>
       <c r="D25" s="52">
         <v>46279</v>
@@ -5429,7 +5438,7 @@
         <v>13</v>
       </c>
       <c r="G25" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H25" s="38" t="s">
         <v>14</v>
@@ -5488,10 +5497,10 @@
         <v>60</v>
       </c>
       <c r="B26" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>146</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>147</v>
       </c>
       <c r="D26" s="47">
         <v>46279</v>
@@ -5503,7 +5512,7 @@
         <v>13</v>
       </c>
       <c r="G26" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H26" s="38" t="s">
         <v>14</v>
@@ -5562,10 +5571,10 @@
         <v>62</v>
       </c>
       <c r="B27" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="28" t="s">
         <v>149</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>150</v>
       </c>
       <c r="D27" s="47">
         <v>46279</v>
@@ -5577,7 +5586,7 @@
         <v>13</v>
       </c>
       <c r="G27" s="49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H27" s="38" t="s">
         <v>14</v>
@@ -5636,10 +5645,10 @@
         <v>64</v>
       </c>
       <c r="B28" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="28" t="s">
         <v>151</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>152</v>
       </c>
       <c r="D28" s="47">
         <v>46279</v>
@@ -5651,7 +5660,7 @@
         <v>13</v>
       </c>
       <c r="G28" s="49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H28" s="38" t="s">
         <v>14</v>
@@ -32958,16 +32967,16 @@
   <sheetData>
     <row r="1" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="D1" s="23" t="s">
         <v>156</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>157</v>
       </c>
       <c r="E1" s="24"/>
       <c r="F1" s="24"/>
@@ -32981,10 +32990,10 @@
         <v>46231</v>
       </c>
       <c r="C2" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>158</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -32995,10 +33004,10 @@
         <v>46233</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>160</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33009,10 +33018,10 @@
         <v>46237</v>
       </c>
       <c r="C4" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>162</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33023,10 +33032,10 @@
         <v>46239</v>
       </c>
       <c r="C5" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>164</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33037,10 +33046,10 @@
         <v>46247</v>
       </c>
       <c r="C6" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="28" t="s">
         <v>166</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33051,10 +33060,10 @@
         <v>46251</v>
       </c>
       <c r="C7" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>168</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33065,10 +33074,10 @@
         <v>46253</v>
       </c>
       <c r="C8" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>170</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33079,10 +33088,10 @@
         <v>46255</v>
       </c>
       <c r="C9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>172</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33093,10 +33102,10 @@
         <v>46265</v>
       </c>
       <c r="C10" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>174</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33107,10 +33116,10 @@
         <v>46267</v>
       </c>
       <c r="C11" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="28" t="s">
         <v>176</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33121,10 +33130,10 @@
         <v>46272</v>
       </c>
       <c r="C12" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>178</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -33135,66 +33144,66 @@
         <v>46274</v>
       </c>
       <c r="C13" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="14" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
-        <v>182</v>
+      <c r="A14" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="B14" s="55">
         <v>46279</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
-        <v>182</v>
+      <c r="A15" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="B15" s="55">
         <v>46280</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>182</v>
+      <c r="A16" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="B16" s="55">
         <v>46281</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
-        <v>182</v>
+      <c r="A17" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="B17" s="55">
         <v>46282</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+      <c r="D17" s="67" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -34183,7 +34192,7 @@
   </sheetData>
   <autoFilter ref="A1:D17" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34206,32 +34215,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="25"/>
+      <c r="B1" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="F1" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="G1" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="H1" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="I1" s="25" t="s">
         <v>195</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>199</v>
       </c>
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
@@ -34268,16 +34275,16 @@
         <v>13</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34297,16 +34304,16 @@
         <v>13</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34326,16 +34333,16 @@
         <v>13</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34355,16 +34362,16 @@
         <v>13</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34384,16 +34391,16 @@
         <v>13</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34413,16 +34420,16 @@
         <v>13</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34442,16 +34449,16 @@
         <v>13</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34471,16 +34478,16 @@
         <v>13</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34500,16 +34507,16 @@
         <v>13</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34529,16 +34536,16 @@
         <v>13</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34558,16 +34565,16 @@
         <v>13</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -34587,24 +34594,24 @@
         <v>13</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>13</v>
       </c>
-      <c r="B14" s="36" t="s">
-        <v>182</v>
+      <c r="B14" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="C14" s="54">
         <v>46279</v>
@@ -34616,24 +34623,24 @@
         <v>13</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>14</v>
       </c>
-      <c r="B15" s="36" t="s">
-        <v>182</v>
+      <c r="B15" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="54">
         <v>46279</v>
@@ -34645,24 +34652,24 @@
         <v>13</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>15</v>
       </c>
-      <c r="B16" s="36" t="s">
-        <v>182</v>
+      <c r="B16" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="C16" s="54">
         <v>46279</v>
@@ -34674,24 +34681,24 @@
         <v>13</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="115.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>16</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>182</v>
+      <c r="B17" s="68" t="s">
+        <v>45</v>
       </c>
       <c r="C17" s="54">
         <v>46279</v>
@@ -34703,16 +34710,16 @@
         <v>13</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G17" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="I17" s="67" t="s">
         <v>261</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
